--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="624" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4EF985E-CD75-4042-B646-D8CB0BDEFB57}"/>
+  <xr:revisionPtr revIDLastSave="650" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08D2B878-2851-484A-B831-B0BA07F77EA7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="sa" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sa!$A$3:$V$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sa!$A$3:$V$49</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="301">
   <si>
     <t>대상설비명</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -2546,10 +2546,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>임시조치 한 상태임,  추후 가공제품 소손시  부품 교체 예정 임</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve"> 5</t>
     </r>
@@ -2880,10 +2876,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>임시조치(프라스틱 자체가공 부착)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>설비</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -3032,6 +3024,26 @@
       </rPr>
       <t>)</t>
     </r>
+  </si>
+  <si>
+    <t>예정</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>셀렉터 스위치 부품 주문 --&gt; 교체 예정</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>부품 주문 완료(셀렉터 스위치)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 가공 된 블록 파손 됨 (현재 사용 불가 임_26년9월29일 현재) </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">부품 도착후 이준열 차장 지원 도움으로 교체 진행 예정 임 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3345,10 +3357,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -3587,10 +3595,10 @@
         <v>11</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>272</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>273</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>41</v>
@@ -3632,19 +3640,19 @@
         <v>14</v>
       </c>
       <c r="Q3" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="R3" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="R3" s="11" t="s">
-        <v>279</v>
-      </c>
       <c r="S3" s="34" t="s">
+        <v>274</v>
+      </c>
+      <c r="T3" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="T3" s="11" t="s">
+      <c r="U3" s="34" t="s">
         <v>276</v>
-      </c>
-      <c r="U3" s="34" t="s">
-        <v>277</v>
       </c>
       <c r="V3" s="11" t="s">
         <v>10</v>
@@ -5183,7 +5191,7 @@
       <c r="T30" s="8"/>
       <c r="U30" s="35"/>
       <c r="V30" s="28" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5589,7 +5597,7 @@
       <c r="T37" s="8"/>
       <c r="U37" s="35"/>
       <c r="V37" s="15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="38" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5647,7 +5655,7 @@
       <c r="T38" s="8"/>
       <c r="U38" s="35"/>
       <c r="V38" s="15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="39" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5705,7 +5713,7 @@
       <c r="T39" s="8"/>
       <c r="U39" s="35"/>
       <c r="V39" s="30" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="40" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5716,7 +5724,7 @@
         <v>45827</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>182</v>
@@ -5821,7 +5829,7 @@
       <c r="T41" s="8"/>
       <c r="U41" s="35"/>
       <c r="V41" s="30" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="42" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5879,7 +5887,7 @@
       <c r="T42" s="8"/>
       <c r="U42" s="35"/>
       <c r="V42" s="30" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="43" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6076,7 +6084,7 @@
         <v>261</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>61</v>
@@ -6103,11 +6111,9 @@
         <v>22</v>
       </c>
       <c r="P46" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q46" s="22" t="s">
-        <v>290</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="Q46" s="22"/>
       <c r="R46" s="22"/>
       <c r="S46" s="36">
         <v>46260</v>
@@ -6115,7 +6121,7 @@
       <c r="T46" s="22"/>
       <c r="U46" s="36"/>
       <c r="V46" s="15" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
     </row>
     <row r="47" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6129,31 +6135,31 @@
         <v>46260</v>
       </c>
       <c r="D47" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="F47" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="G47" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="G47" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="H47" s="3" t="s">
+      <c r="I47" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="I47" s="3" t="s">
+      <c r="J47" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="L47" s="3" t="s">
         <v>284</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>285</v>
       </c>
       <c r="M47" s="6">
         <v>0</v>
@@ -6165,10 +6171,10 @@
         <v>22</v>
       </c>
       <c r="P47" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q47" s="26" t="s">
         <v>286</v>
-      </c>
-      <c r="Q47" s="26" t="s">
-        <v>287</v>
       </c>
       <c r="R47" s="4"/>
       <c r="S47" s="32">
@@ -6189,31 +6195,31 @@
         <v>46265</v>
       </c>
       <c r="D48" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>293</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>40</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="M48" s="6">
         <v>0</v>
@@ -6225,7 +6231,7 @@
         <v>87</v>
       </c>
       <c r="P48" s="31" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q48" s="4"/>
       <c r="R48" s="4"/>
@@ -6233,36 +6239,73 @@
       <c r="T48" s="4"/>
       <c r="U48" s="32"/>
       <c r="V48" s="37" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="49" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="4"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="4"/>
-      <c r="M49" s="6"/>
-      <c r="N49" s="4"/>
-      <c r="O49" s="4"/>
-      <c r="P49" s="4"/>
-      <c r="Q49" s="4"/>
+      <c r="A49" s="4">
+        <v>46</v>
+      </c>
+      <c r="B49" s="7">
+        <v>46294</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="M49" s="6">
+        <v>5500</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P49" s="22" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>298</v>
+      </c>
       <c r="R49" s="4"/>
-      <c r="S49" s="32"/>
+      <c r="S49" s="32">
+        <v>46294</v>
+      </c>
       <c r="T49" s="4"/>
       <c r="U49" s="32"/>
-      <c r="V49" s="1"/>
+      <c r="V49" s="15" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="50" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
-      <c r="B50" s="7"/>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
       <c r="E50" s="4"/>
@@ -7372,9 +7415,9 @@
     <row r="998" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="999" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A3:V13" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A3:V49" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0" right="0" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
+  <pageSetup scale="45" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="650" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08D2B878-2851-484A-B831-B0BA07F77EA7}"/>
+  <xr:revisionPtr revIDLastSave="672" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51A5DAB7-626A-4AEC-BF04-2102C7E61999}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="308">
   <si>
     <t>대상설비명</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -3042,7 +3042,125 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">부품 도착후 이준열 차장 지원 도움으로 교체 진행 예정 임 </t>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>층</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>남자화장실</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>층</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>남자화장실 전등교체</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-30</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">전원 나감 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안정기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">고장 </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">전등 교체 1개(기존 제품 활용) </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>부품호환성 문제 (이차장 해결 함)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>부품 도착후 이준열 차장 지원 도움으로 교체 진행 예정 임 --&gt; 교체 완료(26.10.13)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -3577,7 +3695,7 @@
     <col min="16" max="16" width="14.28515625" style="20" customWidth="1"/>
     <col min="17" max="18" width="30.28515625" style="20" customWidth="1"/>
     <col min="19" max="19" width="30.28515625" style="33" customWidth="1"/>
-    <col min="20" max="20" width="30.28515625" style="20" customWidth="1"/>
+    <col min="20" max="20" width="32.7109375" style="20" customWidth="1"/>
     <col min="21" max="21" width="30.28515625" style="33" customWidth="1"/>
     <col min="22" max="22" width="87.85546875" customWidth="1"/>
     <col min="23" max="35" width="6.5703125" customWidth="1"/>
@@ -6249,8 +6367,8 @@
       <c r="B49" s="7">
         <v>46294</v>
       </c>
-      <c r="C49" s="13" t="s">
-        <v>296</v>
+      <c r="C49" s="13">
+        <v>46308</v>
       </c>
       <c r="D49" s="13" t="s">
         <v>42</v>
@@ -6298,28 +6416,65 @@
       <c r="S49" s="32">
         <v>46294</v>
       </c>
-      <c r="T49" s="4"/>
-      <c r="U49" s="32"/>
+      <c r="T49" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="U49" s="32">
+        <v>46308</v>
+      </c>
       <c r="V49" s="15" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
     </row>
     <row r="50" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="4"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="6"/>
-      <c r="N50" s="4"/>
-      <c r="O50" s="4"/>
-      <c r="P50" s="4"/>
+      <c r="A50" s="4">
+        <v>47</v>
+      </c>
+      <c r="B50" s="18">
+        <v>46308</v>
+      </c>
+      <c r="C50" s="7">
+        <v>46309</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="J50" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="M50" s="6">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P50" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="Q50" s="4"/>
       <c r="R50" s="4"/>
       <c r="S50" s="32"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="672" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51A5DAB7-626A-4AEC-BF04-2102C7E61999}"/>
+  <xr:revisionPtr revIDLastSave="675" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2BFF229-8475-4DC5-A734-7EA2E5013B49}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="310">
   <si>
     <t>대상설비명</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -3161,6 +3161,38 @@
   </si>
   <si>
     <t>부품 도착후 이준열 차장 지원 도움으로 교체 진행 예정 임 --&gt; 교체 완료(26.10.13)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년 9월분 부터 반영</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> 26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년 9월분 부터 반영</t>
+    </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -3475,6 +3507,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -6298,9 +6334,15 @@
       <c r="S47" s="32">
         <v>46260</v>
       </c>
-      <c r="T47" s="4"/>
-      <c r="U47" s="32"/>
-      <c r="V47" s="1"/>
+      <c r="T47" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="U47" s="32">
+        <v>46295</v>
+      </c>
+      <c r="V47" s="27" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="48" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="675" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2BFF229-8475-4DC5-A734-7EA2E5013B49}"/>
+  <xr:revisionPtr revIDLastSave="679" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D2BB629-30BF-4CD7-8B5D-9E0F2BD02017}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="309">
   <si>
     <t>대상설비명</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -3024,10 +3024,6 @@
       </rPr>
       <t>)</t>
     </r>
-  </si>
-  <si>
-    <t>예정</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>셀렉터 스위치 부품 주문 --&gt; 교체 예정</t>
@@ -6264,7 +6260,7 @@
       <c r="O46" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="P46" s="22" t="s">
+      <c r="P46" s="8" t="s">
         <v>23</v>
       </c>
       <c r="Q46" s="22"/>
@@ -6273,9 +6269,11 @@
         <v>46260</v>
       </c>
       <c r="T46" s="22"/>
-      <c r="U46" s="36"/>
+      <c r="U46" s="36">
+        <v>46295</v>
+      </c>
       <c r="V46" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="47" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6335,13 +6333,13 @@
         <v>46260</v>
       </c>
       <c r="T47" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="U47" s="32">
         <v>46295</v>
       </c>
       <c r="V47" s="27" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="48" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6437,7 +6435,7 @@
         <v>19</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M49" s="6">
         <v>5500</v>
@@ -6448,24 +6446,24 @@
       <c r="O49" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="P49" s="22" t="s">
-        <v>296</v>
+      <c r="P49" s="31" t="s">
+        <v>285</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="R49" s="4"/>
       <c r="S49" s="32">
         <v>46294</v>
       </c>
       <c r="T49" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="U49" s="32">
         <v>46308</v>
       </c>
       <c r="V49" s="15" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="50" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6482,28 +6480,28 @@
         <v>42</v>
       </c>
       <c r="E50" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="G50" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>40</v>
       </c>
       <c r="I50" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="J50" s="5" t="s">
         <v>303</v>
-      </c>
-      <c r="J50" s="5" t="s">
-        <v>304</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="M50" s="6">
         <v>0</v>
@@ -6514,8 +6512,8 @@
       <c r="O50" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="P50" s="3" t="s">
-        <v>23</v>
+      <c r="P50" s="31" t="s">
+        <v>285</v>
       </c>
       <c r="Q50" s="4"/>
       <c r="R50" s="4"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="679" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D2BB629-30BF-4CD7-8B5D-9E0F2BD02017}"/>
+  <xr:revisionPtr revIDLastSave="682" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A65C2788-6BA2-45D0-9F90-413B8F96505E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="308">
   <si>
     <t>대상설비명</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -955,14 +955,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>부품교체요망</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>임시조치</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>WD - 40</t>
     </r>
@@ -3189,6 +3181,10 @@
       </rPr>
       <t>년 9월분 부터 반영</t>
     </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>부품교체요망  (이사님 화장실 부품 상호 교체_  부레 핀 교체 진행 완료)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -3745,10 +3741,10 @@
         <v>11</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>41</v>
@@ -3790,19 +3786,19 @@
         <v>14</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="R3" s="11" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="S3" s="34" t="s">
+        <v>272</v>
+      </c>
+      <c r="T3" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="U3" s="34" t="s">
         <v>274</v>
-      </c>
-      <c r="T3" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="U3" s="34" t="s">
-        <v>276</v>
       </c>
       <c r="V3" s="11" t="s">
         <v>10</v>
@@ -4219,7 +4215,7 @@
         <v>72</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>73</v>
@@ -4407,7 +4403,7 @@
         <v>69</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M14" s="6">
         <v>50</v>
@@ -4476,8 +4472,8 @@
       <c r="O15" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="P15" s="22" t="s">
-        <v>109</v>
+      <c r="P15" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="Q15" s="22"/>
       <c r="R15" s="22"/>
@@ -4485,7 +4481,7 @@
       <c r="T15" s="22"/>
       <c r="U15" s="36"/>
       <c r="V15" s="15" t="s">
-        <v>108</v>
+        <v>307</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4502,28 +4498,28 @@
         <v>57</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>61</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>69</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M16" s="6">
         <v>0</v>
@@ -4555,31 +4551,31 @@
         <v>46116</v>
       </c>
       <c r="D17" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="F17" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>61</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>69</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M17" s="6">
         <v>30000</v>
@@ -4614,28 +4610,28 @@
         <v>57</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>61</v>
       </c>
       <c r="I18" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="M18" s="6">
         <v>0</v>
@@ -4644,7 +4640,7 @@
         <v>21</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="P18" s="8" t="s">
         <v>23</v>
@@ -4655,7 +4651,7 @@
       <c r="T18" s="8"/>
       <c r="U18" s="35"/>
       <c r="V18" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4669,31 +4665,31 @@
         <v>46219</v>
       </c>
       <c r="D19" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E19" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="H19" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I19" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="K19" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="L19" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M19" s="6">
         <v>200000</v>
@@ -4728,28 +4724,28 @@
         <v>43</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F20" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="I20" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M20" s="6">
         <v>400000</v>
@@ -4784,28 +4780,28 @@
         <v>57</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>61</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>69</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M21" s="6">
         <v>0</v>
@@ -4825,7 +4821,7 @@
       <c r="T21" s="8"/>
       <c r="U21" s="35"/>
       <c r="V21" s="16" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4839,31 +4835,31 @@
         <v>46231</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F22" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>61</v>
       </c>
       <c r="I22" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="L22" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="M22" s="6">
         <v>0</v>
@@ -4889,37 +4885,37 @@
         <v>20</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C23" s="24">
         <v>46235</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="I23" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="K23" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="L23" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>158</v>
       </c>
       <c r="M23" s="6">
         <v>0</v>
@@ -4928,7 +4924,7 @@
         <v>86</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P23" s="8" t="s">
         <v>23</v>
@@ -4951,31 +4947,31 @@
         <v>46244</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F24" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H24" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="I24" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="H24" s="25" t="s">
+      <c r="J24" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="L24" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>164</v>
       </c>
       <c r="M24" s="6">
         <v>2100000</v>
@@ -5007,31 +5003,31 @@
         <v>46242</v>
       </c>
       <c r="D25" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="G25" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>40</v>
       </c>
       <c r="I25" s="26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="M25" s="6">
         <v>150000</v>
@@ -5040,7 +5036,7 @@
         <v>86</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="P25" s="8" t="s">
         <v>23</v>
@@ -5051,7 +5047,7 @@
       <c r="T25" s="8"/>
       <c r="U25" s="35"/>
       <c r="V25" s="27" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -5068,28 +5064,28 @@
         <v>42</v>
       </c>
       <c r="E26" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="I26" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="H26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="K26" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="L26" s="5" t="s">
         <v>177</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>179</v>
       </c>
       <c r="M26" s="6">
         <v>18000</v>
@@ -5109,7 +5105,7 @@
       <c r="T26" s="8"/>
       <c r="U26" s="35"/>
       <c r="V26" s="27" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -5123,31 +5119,31 @@
         <v>44558</v>
       </c>
       <c r="D27" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>40</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M27" s="6">
         <v>0</v>
@@ -5167,7 +5163,7 @@
       <c r="T27" s="8"/>
       <c r="U27" s="35"/>
       <c r="V27" s="15" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -5181,31 +5177,31 @@
         <v>44558</v>
       </c>
       <c r="D28" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>40</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J28" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="L28" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="M28" s="6">
         <v>0</v>
@@ -5225,7 +5221,7 @@
       <c r="T28" s="8"/>
       <c r="U28" s="35"/>
       <c r="V28" s="28" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -5242,28 +5238,28 @@
         <v>42</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>40</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M29" s="6">
         <v>0</v>
@@ -5283,7 +5279,7 @@
       <c r="T29" s="8"/>
       <c r="U29" s="35"/>
       <c r="V29" s="28" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -5300,28 +5296,28 @@
         <v>42</v>
       </c>
       <c r="E30" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>40</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M30" s="6">
         <v>0</v>
@@ -5341,7 +5337,7 @@
       <c r="T30" s="8"/>
       <c r="U30" s="35"/>
       <c r="V30" s="28" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5355,31 +5351,31 @@
         <v>44838</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F31" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="J31" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="H31" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="I31" s="2" t="s">
+      <c r="K31" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="L31" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="M31" s="6">
         <v>1000000</v>
@@ -5399,7 +5395,7 @@
       <c r="T31" s="8"/>
       <c r="U31" s="35"/>
       <c r="V31" s="29" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5416,28 +5412,28 @@
         <v>42</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>40</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="M32" s="6">
         <v>0</v>
@@ -5457,7 +5453,7 @@
       <c r="T32" s="8"/>
       <c r="U32" s="35"/>
       <c r="V32" s="15" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5474,28 +5470,28 @@
         <v>42</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>40</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="M33" s="6">
         <v>0</v>
@@ -5515,7 +5511,7 @@
       <c r="T33" s="8"/>
       <c r="U33" s="35"/>
       <c r="V33" s="15" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5532,28 +5528,28 @@
         <v>42</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>40</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="M34" s="6">
         <v>0</v>
@@ -5573,7 +5569,7 @@
       <c r="T34" s="8"/>
       <c r="U34" s="35"/>
       <c r="V34" s="15" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="35" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5587,31 +5583,31 @@
         <v>44940</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>40</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L35" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="M35" s="6">
         <v>0</v>
@@ -5631,7 +5627,7 @@
       <c r="T35" s="8"/>
       <c r="U35" s="35"/>
       <c r="V35" s="15" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5645,31 +5641,31 @@
         <v>44941</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>40</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K36" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="M36" s="6">
         <v>0</v>
@@ -5689,7 +5685,7 @@
       <c r="T36" s="8"/>
       <c r="U36" s="35"/>
       <c r="V36" s="15" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="37" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5703,31 +5699,31 @@
         <v>44944</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E37" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>40</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K37" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="M37" s="6">
         <v>0</v>
@@ -5747,7 +5743,7 @@
       <c r="T37" s="8"/>
       <c r="U37" s="35"/>
       <c r="V37" s="15" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="38" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5761,31 +5757,31 @@
         <v>44944</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>40</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K38" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="M38" s="6">
         <v>0</v>
@@ -5805,7 +5801,7 @@
       <c r="T38" s="8"/>
       <c r="U38" s="35"/>
       <c r="V38" s="15" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="39" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5819,31 +5815,31 @@
         <v>45751</v>
       </c>
       <c r="D39" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="E39" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="H39" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="M39" s="6">
         <v>400000</v>
@@ -5863,7 +5859,7 @@
       <c r="T39" s="8"/>
       <c r="U39" s="35"/>
       <c r="V39" s="30" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="40" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5874,34 +5870,34 @@
         <v>45827</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="M40" s="6">
         <v>400000</v>
@@ -5921,7 +5917,7 @@
       <c r="T40" s="8"/>
       <c r="U40" s="35"/>
       <c r="V40" s="30" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="41" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5935,31 +5931,31 @@
         <v>46261</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F41" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="I41" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="J41" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="I41" s="2" t="s">
+      <c r="K41" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="L41" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="M41" s="6">
         <v>400000</v>
@@ -5979,7 +5975,7 @@
       <c r="T41" s="8"/>
       <c r="U41" s="35"/>
       <c r="V41" s="30" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="42" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5993,31 +5989,31 @@
         <v>46261</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I42" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="L42" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="M42" s="6">
         <v>400000</v>
@@ -6037,7 +6033,7 @@
       <c r="T42" s="8"/>
       <c r="U42" s="35"/>
       <c r="V42" s="30" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="43" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6051,31 +6047,31 @@
         <v>46246</v>
       </c>
       <c r="D43" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="G43" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H43" s="25" t="s">
         <v>232</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="I43" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="G43" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="H43" s="25" t="s">
+      <c r="J43" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I43" s="3" t="s">
+      <c r="K43" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="J43" s="3" t="s">
+      <c r="L43" s="3" t="s">
         <v>236</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>238</v>
       </c>
       <c r="M43" s="6">
         <v>0</v>
@@ -6095,7 +6091,7 @@
       <c r="T43" s="8"/>
       <c r="U43" s="35"/>
       <c r="V43" s="27" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="44" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6109,31 +6105,31 @@
         <v>46248</v>
       </c>
       <c r="D44" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="F44" s="3" t="s">
+      <c r="G44" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="H44" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="H44" s="3" t="s">
+      <c r="J44" s="5" t="s">
         <v>245</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="J44" s="5" t="s">
-        <v>247</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>61</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="M44" s="6">
         <v>0</v>
@@ -6153,7 +6149,7 @@
       <c r="T44" s="8"/>
       <c r="U44" s="35"/>
       <c r="V44" s="27" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="45" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6167,31 +6163,31 @@
         <v>46252</v>
       </c>
       <c r="D45" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F45" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="G45" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="H45" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="I45" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="H45" s="3" t="s">
+      <c r="J45" s="3" t="s">
         <v>254</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="K45" s="5" t="s">
         <v>77</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M45" s="6">
         <v>0</v>
@@ -6211,7 +6207,7 @@
       <c r="T45" s="8"/>
       <c r="U45" s="35"/>
       <c r="V45" s="27" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="46" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6225,31 +6221,31 @@
         <v>46260</v>
       </c>
       <c r="D46" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F46" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>261</v>
-      </c>
       <c r="G46" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>61</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>61</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="M46" s="6">
         <v>0</v>
@@ -6273,7 +6269,7 @@
         <v>46295</v>
       </c>
       <c r="V46" s="15" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="47" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6287,31 +6283,31 @@
         <v>46260</v>
       </c>
       <c r="D47" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="G47" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="I47" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="G47" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="H47" s="3" t="s">
+      <c r="J47" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="L47" s="3" t="s">
         <v>282</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>284</v>
       </c>
       <c r="M47" s="6">
         <v>0</v>
@@ -6323,23 +6319,23 @@
         <v>22</v>
       </c>
       <c r="P47" s="31" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="Q47" s="26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="R47" s="4"/>
       <c r="S47" s="32">
         <v>46260</v>
       </c>
       <c r="T47" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="U47" s="32">
         <v>46295</v>
       </c>
       <c r="V47" s="27" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="48" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6353,31 +6349,31 @@
         <v>46265</v>
       </c>
       <c r="D48" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>40</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="M48" s="6">
         <v>0</v>
@@ -6389,7 +6385,7 @@
         <v>87</v>
       </c>
       <c r="P48" s="31" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="Q48" s="4"/>
       <c r="R48" s="4"/>
@@ -6397,7 +6393,7 @@
       <c r="T48" s="4"/>
       <c r="U48" s="32"/>
       <c r="V48" s="37" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="49" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6414,28 +6410,28 @@
         <v>42</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>100</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="M49" s="6">
         <v>5500</v>
@@ -6447,23 +6443,23 @@
         <v>22</v>
       </c>
       <c r="P49" s="31" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="R49" s="4"/>
       <c r="S49" s="32">
         <v>46294</v>
       </c>
       <c r="T49" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="U49" s="32">
         <v>46308</v>
       </c>
       <c r="V49" s="15" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="50" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6480,28 +6476,28 @@
         <v>42</v>
       </c>
       <c r="E50" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="G50" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>301</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>40</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="M50" s="6">
         <v>0</v>
@@ -6513,7 +6509,7 @@
         <v>22</v>
       </c>
       <c r="P50" s="31" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="Q50" s="4"/>
       <c r="R50" s="4"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="682" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A65C2788-6BA2-45D0-9F90-413B8F96505E}"/>
+  <xr:revisionPtr revIDLastSave="699" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6603475-593C-46F8-8484-159D6EDDE324}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="313">
   <si>
     <t>대상설비명</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -3185,6 +3185,66 @@
   </si>
   <si>
     <t>부품교체요망  (이사님 화장실 부품 상호 교체_  부레 핀 교체 진행 완료)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>층 설비실 수전</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-31</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">물이 샘 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">고무 마모로 인한 누수 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>와사고정 체결+ 고무패킹(2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t>mm)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추가</t>
+    </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -6519,22 +6579,54 @@
       <c r="V50" s="1"/>
     </row>
     <row r="51" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="4"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="6"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
-      <c r="P51" s="4"/>
+      <c r="A51" s="4">
+        <v>48</v>
+      </c>
+      <c r="B51" s="7">
+        <v>46318</v>
+      </c>
+      <c r="C51" s="7">
+        <v>46318</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L51" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="M51" s="6">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="P51" s="31" t="s">
+        <v>283</v>
+      </c>
       <c r="Q51" s="4"/>
       <c r="R51" s="4"/>
       <c r="S51" s="32"/>
